--- a/output/graficos_educacion_tasas/comunal_e_rezjov_a_2018_metropolitana.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezjov_a_2018_metropolitana.xlsx
@@ -189,7 +189,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:27</t>
+    <t xml:space="preserve">2026-09-09 20:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_rezjov_a_2018_metropolitana.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezjov_a_2018_metropolitana.xlsx
@@ -24,162 +24,162 @@
     <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
+    <t xml:space="preserve">Santiago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerrillos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerro Navia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conchalí</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Bosque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estación Central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huechuraba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Cisterna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Florida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Granja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Pintana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Reina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las Condes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Barnechea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Espejo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Prado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maipú</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ñuñoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedro Aguirre Cerda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peñalolén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Providencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pudahuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilicura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinta Normal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recoleta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Joaquín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Miguel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Ramón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vitacura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puente Alto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pirque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San José de Maipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lampa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiltil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Bernardo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calera de Tango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melipilla</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alhué</t>
   </si>
   <si>
-    <t xml:space="preserve">Buin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calera de Tango</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerrillos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerro Navia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conchalí</t>
-  </si>
-  <si>
     <t xml:space="preserve">Curacaví</t>
   </si>
   <si>
-    <t xml:space="preserve">El Bosque</t>
+    <t xml:space="preserve">María Pinto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Pedro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talagante</t>
   </si>
   <si>
     <t xml:space="preserve">El Monte</t>
   </si>
   <si>
-    <t xml:space="preserve">Estación Central</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Huechuraba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Independencia</t>
-  </si>
-  <si>
     <t xml:space="preserve">Isla de Maipo</t>
   </si>
   <si>
-    <t xml:space="preserve">La Cisterna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Florida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Granja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Pintana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Reina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lampa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las Condes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo Barnechea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo Espejo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo Prado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Macul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maipú</t>
-  </si>
-  <si>
-    <t xml:space="preserve">María Pinto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melipilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ñuñoa</t>
-  </si>
-  <si>
     <t xml:space="preserve">Padre Hurtado</t>
   </si>
   <si>
-    <t xml:space="preserve">Paine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pedro Aguirre Cerda</t>
-  </si>
-  <si>
     <t xml:space="preserve">Peñaflor</t>
   </si>
   <si>
-    <t xml:space="preserve">Peñalolén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pirque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Providencia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pudahuel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puente Alto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quilicura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quinta Normal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recoleta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Bernardo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Joaquín</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San José de Maipo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Miguel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Pedro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Ramón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santiago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talagante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiltil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vitacura</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -189,7 +189,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:26</t>
+    <t xml:space="preserve">2026-09-18 10:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -601,7 +601,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>3.21</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="3">
@@ -609,7 +609,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>4.54</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="4">
@@ -617,7 +617,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2.16</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="5">
@@ -625,7 +625,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4.88</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>4.6</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="7">
@@ -641,7 +641,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>3.93</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="8">
@@ -649,7 +649,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>5.01</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="9">
@@ -657,7 +657,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>4.21</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="10">
@@ -665,7 +665,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>4.64</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="11">
@@ -673,7 +673,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>3.65</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="12">
@@ -681,7 +681,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>4.22</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="13">
@@ -689,7 +689,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>3.74</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="14">
@@ -697,7 +697,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2.98</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="15">
@@ -705,7 +705,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>4.5</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="16">
@@ -713,7 +713,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>3.37</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="17">
@@ -721,7 +721,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>3.96</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="18">
@@ -729,7 +729,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="19">
@@ -737,7 +737,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>6.31</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="20">
@@ -745,7 +745,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>2.51</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="21">
@@ -753,7 +753,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>4.42</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="22">
@@ -761,7 +761,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>1.66</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="23">
@@ -769,7 +769,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>2.35</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="24">
@@ -777,7 +777,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>5.21</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="25">
@@ -785,7 +785,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>4.8</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="26">
@@ -793,7 +793,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>4.24</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="27">
@@ -801,7 +801,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>3.93</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="28">
@@ -809,7 +809,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>2.79</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="29">
@@ -817,7 +817,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>3.8</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="30">
@@ -825,7 +825,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>2.16</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="31">
@@ -833,7 +833,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>3.91</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="32">
@@ -841,7 +841,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>4.04</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="33">
@@ -849,7 +849,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>4.36</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -857,7 +857,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>3.33</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="35">
@@ -865,7 +865,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>4.57</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="36">
@@ -873,7 +873,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="37">
@@ -881,7 +881,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>1.35</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="38">
@@ -889,7 +889,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>3.89</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="39">
@@ -897,7 +897,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>4.78</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="40">
@@ -905,7 +905,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>3.88</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="41">
@@ -913,7 +913,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>3.89</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="42">
@@ -921,7 +921,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>4.41</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="43">
@@ -929,7 +929,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>4.61</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="44">
@@ -937,7 +937,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>4.35</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="45">
@@ -945,7 +945,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>4.23</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="46">
@@ -953,7 +953,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>3.75</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="47">
@@ -961,7 +961,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="48">
@@ -977,7 +977,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>5.32</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="50">
@@ -985,7 +985,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>3.03</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="51">
@@ -993,7 +993,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>3.37</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="52">
@@ -1001,7 +1001,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>4.41</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="53">
@@ -1009,7 +1009,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>1</v>
+        <v>3.33</v>
       </c>
     </row>
   </sheetData>
